--- a/static/薪酬诊断数据收集模板.xlsx
+++ b/static/薪酬诊断数据收集模板.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,20 @@
     </font>
     <font>
       <color rgb="0094A3B8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000A66C2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000A66C2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -67,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -89,11 +103,55 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,11 +165,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -487,18 +554,19 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -534,71 +602,76 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>月度基本工资（必填）</t>
+          <t>年度基本工资（必填）</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>年终奖（年度）（必填）</t>
+          <t>年固定奖金（必填）</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>13薪（如有）</t>
+          <t>年浮动奖金</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>各类现金津贴（月度）</t>
+          <t>年现金津贴</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>年津贴报销</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>年度绩效结果</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>入司时间</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>直属上级工号/姓名</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>管理岗/专业岗</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>是否关键岗位</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>管理复杂度</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Base 城市</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>年龄</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>教育背景</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>用于标识员工个体</t>
@@ -631,65 +704,70 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>税前固定月薪，单位：元</t>
+          <t>年度税前基本工资，单位：元。如按月发放请×12</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>上一年度实际发放的年终奖，单位：元</t>
+          <t>含13薪、年节礼金、年定额奖金等固定发放的年度奖金，单位：元。不含绩效浮动部分</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>如有固定13薪请单独填写，单位：元</t>
+          <t>与绩效挂钩的浮动奖金，含绩效奖金、销售佣金、利润分红等，单位：元。填实际发放金额</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>交通补贴、餐补等，单位：元/月</t>
+          <t>计入总现金的年度现金津贴总额，含住房、交通、伙食、通讯、岗位、技能等津贴，单位：元</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>如 A/B+/B/B-/C 或 3.75/3.5 等</t>
+          <t>不计入总现金的报销类津贴，如实报实销的差旅、通讯、交通等，单位：元</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>如 A/B+/B/B-/C 或 3.75/3.5/3.25 等</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>格式：YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>用于检查上下级薪酬倒挂</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>下拉选择：管理岗 / 专业岗</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>下拉选择：是 / 否</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>下拉选择：低 / 中 / 高</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>如：北京、上海、深圳</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>数字</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>如：本科、硕士、博士</t>
         </is>
@@ -728,79 +806,94 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>2021-03-15</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>李四 / EMP002</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>管理岗</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>硕士</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>TCC 计算公式：年度现金总薪酬 = 年度基本工资 + 年固定奖金 + 年浮动奖金 + 年现金津贴（不含报销类津贴）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:T4"/>
+  </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="N4:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="请选择" type="list">
+    <dataValidation sqref="O4:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"管理岗,专业岗"</formula1>
     </dataValidation>
-    <dataValidation sqref="O4:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P4:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="P4:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q4:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"低,中,高"</formula1>
     </dataValidation>
   </dataValidations>
@@ -814,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -825,95 +918,99 @@
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>指标名称</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>2022年</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>2024年</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>年度营收（万元）</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>公司全年营业收入</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="6" t="inlineStr"/>
-      <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>年度利润（万元）</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>公司全年净利润</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr"/>
-      <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>一、经营数据（按年填写）</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>员工总人数</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>年末在职员工总数</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>2022年</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>人工成本总额（万元）</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>含工资、奖金、社保、福利等</t>
+          <t>年度营收（万元）</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>公司全年营业收入</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr"/>
@@ -922,46 +1019,517 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>年度营收增长率</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>同比增长百分比，如 20%</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>年度净利润（万元）</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>公司全年净利润</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>年度毛利率</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>毛利/营收，如 25%</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>二、人力资本数据（按年填写）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>2022年</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>员工总人数</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>年末在职员工总数</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>年总薪水支出（万元）</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>全员固定收入+浮动收入总额</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>年总福利支出（万元）</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>含法定社保、补充福利等</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>人工成本总额（万元）</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f> 总薪水 + 总福利 + 招聘培训等</f>
+        <v/>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>年度招聘成本（万元）</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>不含薪酬，仅招聘渠道、人力等</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>年度培训成本（万元）</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>不含薪酬，仅培训费用</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>三、调薪信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>本年度实际</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>下年度预算</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>调薪月份</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>如：1月、4月、7月</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>是否冻薪</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>调薪预算拆分</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>调薪类型</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>本年度实际</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>下年度预算</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>普通调薪</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>全员普调比例</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>绩效调薪</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>根据绩效差异化调薪比例</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>特殊调薪</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>市场对标、留人等专项调薪</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>晋升调薪</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>晋升带来的薪酬调整</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>总计调薪（不含晋升）</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <f> 普通 + 绩效 + 特殊</f>
+        <v/>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>按层级的调薪预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>职位层级</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>本年度实际</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>下年度预算</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>高管层</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>中层管理</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>主管/高级专业</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>一般职员</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>四、部门级绩效结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>部门名称</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>部门级绩效结果</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>部门绩效结果</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr"/>
+      <c r="E41" s="1" t="inlineStr"/>
+      <c r="F41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr"/>
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>如 A/B/C 或达标/未达标</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="11" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr"/>
+      <c r="B44" s="11" t="inlineStr"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr"/>
+      <c r="B45" s="11" t="inlineStr"/>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="11" t="inlineStr"/>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="11" t="inlineStr"/>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr"/>
+      <c r="B48" s="11" t="inlineStr"/>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr"/>
+      <c r="B49" s="11" t="inlineStr"/>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>如 A/B/C 或达标/未达标</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A40:F40"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>